--- a/student_scores.xlsx
+++ b/student_scores.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,21 +417,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -565,6 +574,36 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>Invalid</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>junjun</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>77</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>romulo</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>88</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
